--- a/cet4/result/01_重生商女_豪门弃女逆袭记/01_重生商女_豪门弃女逆袭记_学习版.xlsx
+++ b/cet4/result/01_重生商女_豪门弃女逆袭记/01_重生商女_豪门弃女逆袭记_学习版.xlsx
@@ -397,1039 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>alive</v>
       </c>
       <c r="B2" t="str">
-        <v>alive</v>
+        <v>/əˈlaɪv/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>活着的</v>
       </c>
-      <c r="D2" t="str">
-        <v>alive(活着的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>furniture</v>
       </c>
       <c r="B3" t="str">
-        <v>furniture</v>
+        <v>/ˈfɜːrnɪtʃər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>家具</v>
       </c>
-      <c r="D3" t="str">
-        <v>furniture(家具)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>huge</v>
       </c>
       <c r="B4" t="str">
-        <v>huge</v>
+        <v>/hjuːdʒ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>巨大的</v>
       </c>
-      <c r="D4" t="str">
-        <v>huge(巨大的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>uncle</v>
       </c>
       <c r="B5" t="str">
-        <v>uncle</v>
+        <v>/ˈʌŋkl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>叔叔</v>
       </c>
-      <c r="D5" t="str">
-        <v>uncle(叔叔)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>lumber</v>
       </c>
       <c r="B6" t="str">
-        <v>uncle</v>
+        <v>/ˈlʌmbər/</v>
       </c>
       <c r="C6" t="str">
-        <v>叔叔</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D6" t="str">
-        <v>uncle(叔叔)📢</v>
+        <v>木材</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>fee</v>
       </c>
       <c r="B7" t="str">
-        <v>uncle</v>
+        <v>/fiː/</v>
       </c>
       <c r="C7" t="str">
-        <v>叔叔</v>
+        <v>n./vt.</v>
       </c>
       <c r="D7" t="str">
-        <v>uncle(叔叔)📢</v>
+        <v>费用</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>objective</v>
       </c>
       <c r="B8" t="str">
-        <v>lumber</v>
+        <v>/əbˈdʒektɪv/</v>
       </c>
       <c r="C8" t="str">
-        <v>木材</v>
+        <v>n./adj.</v>
       </c>
       <c r="D8" t="str">
-        <v>lumber(木材)📢</v>
+        <v>目标</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>enable</v>
       </c>
       <c r="B9" t="str">
-        <v>uncle</v>
+        <v>/ɪˈneɪbl/</v>
       </c>
       <c r="C9" t="str">
-        <v>叔叔</v>
+        <v>v.</v>
       </c>
       <c r="D9" t="str">
-        <v>uncle(叔叔)📢</v>
+        <v>使能够</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>suitable</v>
       </c>
       <c r="B10" t="str">
-        <v>lumber</v>
+        <v>/ˈsuːtəbl/</v>
       </c>
       <c r="C10" t="str">
-        <v>木材</v>
+        <v>adj.</v>
       </c>
       <c r="D10" t="str">
-        <v>lumber(木材)📢</v>
+        <v>合适的</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>railway</v>
       </c>
       <c r="B11" t="str">
-        <v>fee</v>
+        <v>/ˈreɪlweɪ/</v>
       </c>
       <c r="C11" t="str">
-        <v>费用</v>
+        <v>n./vi.</v>
       </c>
       <c r="D11" t="str">
-        <v>fee(费用)📢</v>
+        <v>铁路</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>meter</v>
       </c>
       <c r="B12" t="str">
-        <v>lumber</v>
+        <v>/ˈmiːtər/</v>
       </c>
       <c r="C12" t="str">
-        <v>木材</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D12" t="str">
-        <v>lumber(木材)📢</v>
+        <v>米</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>land</v>
       </c>
       <c r="B13" t="str">
-        <v>uncle</v>
+        <v>/lænd/</v>
       </c>
       <c r="C13" t="str">
-        <v>叔叔</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D13" t="str">
-        <v>uncle(叔叔)📢</v>
+        <v>土地</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cheap</v>
       </c>
       <c r="B14" t="str">
-        <v>objective</v>
+        <v>/tʃiːp/</v>
       </c>
       <c r="C14" t="str">
-        <v>目标</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D14" t="str">
-        <v>objective(目标)📢</v>
+        <v>便宜的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>rapidly</v>
       </c>
       <c r="B15" t="str">
-        <v>uncle</v>
+        <v>/ˈræpɪdli/</v>
       </c>
       <c r="C15" t="str">
-        <v>叔叔</v>
+        <v>v./adv.</v>
       </c>
       <c r="D15" t="str">
-        <v>uncle(叔叔)📢</v>
+        <v>迅速地</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>convert</v>
       </c>
       <c r="B16" t="str">
-        <v>enable</v>
+        <v>/kənˈvɜːrt/</v>
       </c>
       <c r="C16" t="str">
-        <v>使能够</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D16" t="str">
-        <v>enable(使能够)📢</v>
+        <v>转变</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>upward</v>
       </c>
       <c r="B17" t="str">
-        <v>suitable</v>
+        <v>/ˈʌpwərd/</v>
       </c>
       <c r="C17" t="str">
-        <v>合适的</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D17" t="str">
-        <v>suitable(合适的)📢</v>
+        <v>向上的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>mistake</v>
       </c>
       <c r="B18" t="str">
-        <v>railway</v>
+        <v>/mɪˈsteɪk/</v>
       </c>
       <c r="C18" t="str">
-        <v>铁路</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D18" t="str">
-        <v>railway(铁路)📢</v>
+        <v>错误</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>rotate</v>
       </c>
       <c r="B19" t="str">
-        <v>meter</v>
+        <v>/ˈroʊteɪt/</v>
       </c>
       <c r="C19" t="str">
-        <v>米</v>
+        <v>vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>meter(米)📢</v>
+        <v>旋转</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>solid</v>
       </c>
       <c r="B20" t="str">
-        <v>land</v>
+        <v>/ˈsɑːlɪd/</v>
       </c>
       <c r="C20" t="str">
-        <v>土地</v>
+        <v>n./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>land(土地)📢</v>
+        <v>可靠的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>scale</v>
       </c>
       <c r="B21" t="str">
-        <v>cheap</v>
+        <v>/skeɪl/</v>
       </c>
       <c r="C21" t="str">
-        <v>便宜的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>cheap(便宜的)📢</v>
+        <v>规模</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>number</v>
       </c>
       <c r="B22" t="str">
-        <v>rapidly</v>
+        <v>/ˈnʌmbər/</v>
       </c>
       <c r="C22" t="str">
-        <v>迅速地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>rapidly(迅速地)📢</v>
+        <v>数字</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>stare</v>
       </c>
       <c r="B23" t="str">
-        <v>convert</v>
+        <v>/ster/</v>
       </c>
       <c r="C23" t="str">
-        <v>转变</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>convert(转变)📢</v>
+        <v>凝视</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>he</v>
       </c>
       <c r="B24" t="str">
-        <v>upward</v>
+        <v>/hi,iː,i,hiː/</v>
       </c>
       <c r="C24" t="str">
-        <v>向上的</v>
+        <v>n./pron.</v>
       </c>
       <c r="D24" t="str">
-        <v>upward(向上的)📢</v>
+        <v>他</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>extensive</v>
       </c>
       <c r="B25" t="str">
-        <v>mistake</v>
+        <v>/ɪkˈstensɪv/</v>
       </c>
       <c r="C25" t="str">
-        <v>错误</v>
+        <v>adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>mistake(错误)📢</v>
+        <v>广泛的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>infer</v>
       </c>
       <c r="B26" t="str">
-        <v>rotate</v>
+        <v>/ɪnˈfɜːr/</v>
       </c>
       <c r="C26" t="str">
-        <v>旋转</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>rotate(旋转)📢</v>
+        <v>推断</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>intentional</v>
       </c>
       <c r="B27" t="str">
-        <v>solid</v>
+        <v>/ɪnˈtenʃənl/</v>
       </c>
       <c r="C27" t="str">
-        <v>可靠的</v>
+        <v>adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>solid(可靠的)📢</v>
+        <v>故意的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>unfair</v>
       </c>
       <c r="B28" t="str">
-        <v>rapidly</v>
+        <v>/ˌʌnˈfer/</v>
       </c>
       <c r="C28" t="str">
-        <v>迅速地</v>
+        <v>adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>rapidly(迅速地)📢</v>
+        <v>不公平的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>liable</v>
       </c>
       <c r="B29" t="str">
-        <v>scale</v>
+        <v>/ˈlaɪəbl/</v>
       </c>
       <c r="C29" t="str">
-        <v>规模</v>
+        <v>adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>scale(规模)📢</v>
+        <v>有责任的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>among</v>
       </c>
       <c r="B30" t="str">
-        <v>number</v>
+        <v>/əˈmʌŋ/</v>
       </c>
       <c r="C30" t="str">
-        <v>数字</v>
+        <v>prep.</v>
       </c>
       <c r="D30" t="str">
-        <v>number(数字)📢</v>
+        <v>在...中间</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>naval</v>
       </c>
       <c r="B31" t="str">
-        <v>stare</v>
+        <v>/ˈneɪvl/</v>
       </c>
       <c r="C31" t="str">
-        <v>凝视</v>
+        <v>n./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>stare(凝视)📢</v>
+        <v>海军的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>flavour</v>
       </c>
       <c r="B32" t="str">
-        <v>he</v>
+        <v>/ˈfleɪvər/</v>
       </c>
       <c r="C32" t="str">
-        <v>他</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>he(他)📢</v>
+        <v>风味</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>important</v>
       </c>
       <c r="B33" t="str">
-        <v>extensive</v>
+        <v>/ɪmˈpɔːrtnt/</v>
       </c>
       <c r="C33" t="str">
-        <v>广泛的</v>
+        <v>adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>extensive(广泛的)📢</v>
+        <v>重要的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>begin</v>
       </c>
       <c r="B34" t="str">
-        <v>infer</v>
+        <v>/bɪˈɡɪn/</v>
       </c>
       <c r="C34" t="str">
-        <v>推断</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>infer(推断)📢</v>
+        <v>开始</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>pollution</v>
       </c>
       <c r="B35" t="str">
-        <v>intentional</v>
+        <v>/pəˈluːʃn/</v>
       </c>
       <c r="C35" t="str">
-        <v>故意的</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>intentional(故意的)📢</v>
+        <v>污染</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>queer</v>
       </c>
       <c r="B36" t="str">
-        <v>unfair</v>
+        <v>/kwɪr/</v>
       </c>
       <c r="C36" t="str">
-        <v>不公平的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>unfair(不公平的)📢</v>
+        <v>奇怪的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>shall</v>
       </c>
       <c r="B37" t="str">
-        <v>liable</v>
+        <v>/ʃəl,ʃæl/</v>
       </c>
       <c r="C37" t="str">
-        <v>有责任的</v>
+        <v>aux.</v>
       </c>
       <c r="D37" t="str">
-        <v>liable(有责任的)📢</v>
+        <v>将</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>inventor</v>
       </c>
       <c r="B38" t="str">
-        <v>among</v>
+        <v>/ɪnˈventər/</v>
       </c>
       <c r="C38" t="str">
-        <v>在...中间</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>among(在...中间)📢</v>
+        <v>发明家</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>gymnasium</v>
       </c>
       <c r="B39" t="str">
-        <v>naval</v>
+        <v>/dʒɪmˈneɪziəm/</v>
       </c>
       <c r="C39" t="str">
-        <v>海军的</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>naval(海军的)📢</v>
+        <v>体育馆</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>fond</v>
       </c>
       <c r="B40" t="str">
-        <v>naval</v>
+        <v>/fɑːnd/</v>
       </c>
       <c r="C40" t="str">
-        <v>海军的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>naval(海军的)📢</v>
+        <v>喜欢的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>hopeless</v>
       </c>
       <c r="B41" t="str">
-        <v>flavour</v>
+        <v>/ˈhoʊpləs/</v>
       </c>
       <c r="C41" t="str">
-        <v>风味</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>flavour(风味)📢</v>
+        <v>绝望的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>pleasant</v>
       </c>
       <c r="B42" t="str">
-        <v>important</v>
+        <v>/ˈpleznt/</v>
       </c>
       <c r="C42" t="str">
-        <v>重要的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>important(重要的)📢</v>
+        <v>令人愉快的</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>vacation</v>
       </c>
       <c r="B43" t="str">
-        <v>begin</v>
+        <v>/veɪˈkeɪʃn/</v>
       </c>
       <c r="C43" t="str">
-        <v>开始</v>
+        <v>n./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>begin(开始)📢</v>
+        <v>假期</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>accommodation</v>
       </c>
       <c r="B44" t="str">
-        <v>lumber</v>
+        <v>/əˌkɑːməˈdeɪʃn/</v>
       </c>
       <c r="C44" t="str">
-        <v>木材</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>lumber(木材)📢</v>
+        <v>住宿</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>liter</v>
       </c>
       <c r="B45" t="str">
-        <v>pollution</v>
+        <v>/ˈliːtər/</v>
       </c>
       <c r="C45" t="str">
-        <v>污染</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>pollution(污染)📢</v>
+        <v>公升</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>cast</v>
       </c>
       <c r="B46" t="str">
-        <v>queer</v>
+        <v>/kæst/</v>
       </c>
       <c r="C46" t="str">
-        <v>奇怪的</v>
+        <v>n./v.</v>
       </c>
       <c r="D46" t="str">
-        <v>queer(奇怪的)📢</v>
+        <v>投掷</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>toe</v>
       </c>
       <c r="B47" t="str">
-        <v>rapidly</v>
+        <v>/toʊ/</v>
       </c>
       <c r="C47" t="str">
-        <v>迅速地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>rapidly(迅速地)📢</v>
+        <v>脚趾</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>cheese</v>
       </c>
       <c r="B48" t="str">
-        <v>shall</v>
+        <v>/tʃiːz/</v>
       </c>
       <c r="C48" t="str">
-        <v>将</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>shall(将)📢</v>
+        <v>奶酪</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>be</v>
       </c>
       <c r="B49" t="str">
-        <v>inventor</v>
+        <v>/bi,biː/</v>
       </c>
       <c r="C49" t="str">
-        <v>发明家</v>
+        <v>n./vt.</v>
       </c>
       <c r="D49" t="str">
-        <v>inventor(发明家)📢</v>
+        <v>是</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>plough</v>
       </c>
       <c r="B50" t="str">
-        <v>furniture</v>
+        <v>/plaʊ/</v>
       </c>
       <c r="C50" t="str">
-        <v>家具</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>furniture(家具)📢</v>
+        <v>犁</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>mental</v>
       </c>
       <c r="B51" t="str">
-        <v>gymnasium</v>
+        <v>/ˈmentl/</v>
       </c>
       <c r="C51" t="str">
-        <v>体育馆</v>
+        <v>n./adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>gymnasium(体育馆)📢</v>
+        <v>精神的</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>inward</v>
       </c>
       <c r="B52" t="str">
-        <v>fond</v>
+        <v>/ˈɪnwərd/</v>
       </c>
       <c r="C52" t="str">
-        <v>喜欢的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D52" t="str">
-        <v>fond(喜欢的)📢</v>
+        <v>向内的</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>trace</v>
       </c>
       <c r="B53" t="str">
-        <v>hopeless</v>
+        <v>/treɪs/</v>
       </c>
       <c r="C53" t="str">
-        <v>绝望的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D53" t="str">
-        <v>hopeless(绝望的)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>pleasant</v>
-      </c>
-      <c r="C54" t="str">
-        <v>令人愉快的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>pleasant(令人愉快的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>alive</v>
-      </c>
-      <c r="C55" t="str">
-        <v>活着的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>alive(活着的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>vacation</v>
-      </c>
-      <c r="C56" t="str">
-        <v>假期</v>
-      </c>
-      <c r="D56" t="str">
-        <v>vacation(假期)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>accommodation</v>
-      </c>
-      <c r="C57" t="str">
-        <v>住宿</v>
-      </c>
-      <c r="D57" t="str">
-        <v>accommodation(住宿)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>liter</v>
-      </c>
-      <c r="C58" t="str">
-        <v>公升</v>
-      </c>
-      <c r="D58" t="str">
-        <v>liter(公升)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>pleasant</v>
-      </c>
-      <c r="C59" t="str">
-        <v>令人愉快的</v>
-      </c>
-      <c r="D59" t="str">
-        <v>pleasant(令人愉快的)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>cast</v>
-      </c>
-      <c r="C60" t="str">
-        <v>投掷</v>
-      </c>
-      <c r="D60" t="str">
-        <v>cast(投掷)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>toe</v>
-      </c>
-      <c r="C61" t="str">
-        <v>脚趾</v>
-      </c>
-      <c r="D61" t="str">
-        <v>toe(脚趾)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>accommodation</v>
-      </c>
-      <c r="C62" t="str">
-        <v>住宿</v>
-      </c>
-      <c r="D62" t="str">
-        <v>accommodation(住宿)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>cheese</v>
-      </c>
-      <c r="C63" t="str">
-        <v>奶酪</v>
-      </c>
-      <c r="D63" t="str">
-        <v>cheese(奶酪)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>scale</v>
-      </c>
-      <c r="C64" t="str">
-        <v>规模</v>
-      </c>
-      <c r="D64" t="str">
-        <v>scale(规模)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>mistake</v>
-      </c>
-      <c r="C65" t="str">
-        <v>错误</v>
-      </c>
-      <c r="D65" t="str">
-        <v>mistake(错误)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>mistake</v>
-      </c>
-      <c r="C66" t="str">
-        <v>错误</v>
-      </c>
-      <c r="D66" t="str">
-        <v>mistake(错误)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>extensive</v>
-      </c>
-      <c r="C67" t="str">
-        <v>广泛的</v>
-      </c>
-      <c r="D67" t="str">
-        <v>extensive(广泛的)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>be</v>
-      </c>
-      <c r="C68" t="str">
-        <v>是</v>
-      </c>
-      <c r="D68" t="str">
-        <v>be(是)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>plough</v>
-      </c>
-      <c r="C69" t="str">
-        <v>犁</v>
-      </c>
-      <c r="D69" t="str">
-        <v>plough(犁)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>mental</v>
-      </c>
-      <c r="C70" t="str">
-        <v>精神的</v>
-      </c>
-      <c r="D70" t="str">
-        <v>mental(精神的)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>inward</v>
-      </c>
-      <c r="C71" t="str">
-        <v>向内的</v>
-      </c>
-      <c r="D71" t="str">
-        <v>inward(向内的)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>uncle</v>
-      </c>
-      <c r="C72" t="str">
-        <v>叔叔</v>
-      </c>
-      <c r="D72" t="str">
-        <v>uncle(叔叔)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>trace</v>
-      </c>
-      <c r="C73" t="str">
         <v>痕迹</v>
-      </c>
-      <c r="D73" t="str">
-        <v>trace(痕迹)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>